--- a/reports/google_workspace_billing_report/templates/xlsx/template.xlsx
+++ b/reports/google_workspace_billing_report/templates/xlsx/template.xlsx
@@ -1,32 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10112"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\filip.djordjevic\source\repos\google-workspace-connect-report\reports\google_workspace_billing_report\templates\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dfranco00/Sites/google-workspace-connect-report/reports/google_workspace_report/templates/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0878B7D-A0AB-4857-9DB6-8A2D0F5A9CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35C4D3B-36EF-284E-9270-5F343FC2D79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4692" yWindow="5412" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="19380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Info" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$AA$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$BA$1</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
-  <si>
-    <t>Month Year</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>Subscription ID</t>
   </si>
@@ -34,7 +32,13 @@
     <t>Subscription External ID</t>
   </si>
   <si>
-    <t>Subscription External UUID</t>
+    <t>Subscription Type</t>
+  </si>
+  <si>
+    <t>Google Domain</t>
+  </si>
+  <si>
+    <t>Google Customer ID</t>
   </si>
   <si>
     <t>Item Name</t>
@@ -43,77 +47,243 @@
     <t>Item MPN</t>
   </si>
   <si>
-    <t>Item Period</t>
-  </si>
-  <si>
-    <t>Quantity</t>
+    <t>Google SKU</t>
+  </si>
+  <si>
+    <t>Google Product</t>
+  </si>
+  <si>
+    <t>Creation date</t>
+  </si>
+  <si>
+    <t>Updated date</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Billing Period</t>
+  </si>
+  <si>
+    <t>Anniversary Day</t>
+  </si>
+  <si>
+    <t>Anniversary Month</t>
+  </si>
+  <si>
+    <t>Contract ID</t>
+  </si>
+  <si>
+    <t>Contract Name</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Customer Name</t>
+  </si>
+  <si>
+    <t>Customer External ID</t>
+  </si>
+  <si>
+    <t>Tier 1 ID</t>
+  </si>
+  <si>
+    <t>Tier 1 Name</t>
+  </si>
+  <si>
+    <t>Tier 1 External ID</t>
+  </si>
+  <si>
+    <t>Tier 2 ID</t>
+  </si>
+  <si>
+    <t>Tier 2 Name</t>
+  </si>
+  <si>
+    <t>Tier 2 External ID</t>
+  </si>
+  <si>
+    <t>Provider Account ID</t>
+  </si>
+  <si>
+    <t>Provider Account name</t>
+  </si>
+  <si>
+    <t>Vendor Account ID</t>
+  </si>
+  <si>
+    <t>Vendor Account Name</t>
+  </si>
+  <si>
+    <t>Product ID</t>
+  </si>
+  <si>
+    <t>Product Name</t>
+  </si>
+  <si>
+    <t>Hub ID</t>
+  </si>
+  <si>
+    <t>Hub Name</t>
+  </si>
+  <si>
+    <t>PA-877-687</t>
+  </si>
+  <si>
+    <t>IM Team MSK test MB</t>
+  </si>
+  <si>
+    <t>Report Execution Information</t>
+  </si>
+  <si>
+    <t>Report Start time</t>
+  </si>
+  <si>
+    <t>2024-02-15 09:14:29</t>
+  </si>
+  <si>
+    <t>Report Finish time</t>
+  </si>
+  <si>
+    <t>2024-02-15 09:14:40</t>
+  </si>
+  <si>
+    <t>Account ID</t>
+  </si>
+  <si>
+    <t>Account Name</t>
+  </si>
+  <si>
+    <t>Report ID</t>
+  </si>
+  <si>
+    <t>google_workspace_report</t>
+  </si>
+  <si>
+    <t>Report Name</t>
+  </si>
+  <si>
+    <t>Google Workspace report</t>
+  </si>
+  <si>
+    <t>Runtime environment</t>
+  </si>
+  <si>
+    <t>Connect Reports</t>
+  </si>
+  <si>
+    <t>Report execution parameters</t>
+  </si>
+  <si>
+    <t>{
+    "connection_type": {
+        "all": true,
+        "choices": []
+    },
+    "date": {
+        "after": "2020-01-01T00:00:00Z",
+        "before": "2024-02-15T23:59:59Z"
+    },
+    "mkp": {
+        "all": true,
+        "choices": [
+            "MP-36329",
+            "MP-71963",
+            "MP-48991",
+            "MP-72850",
+            "MP-45742",
+            "MP-88067",
+            "MP-93375",
+            "MP-27568",
+            "MP-19342",
+            "MP-17843",
+            "MP-64484",
+            "MP-69293",
+            "MP-15639",
+            "MP-19606",
+            "MP-65867",
+            "MP-38262",
+            "MP-83139",
+            "MP-62563",
+            "MP-63034",
+            "MP-63190"
+        ]
+    },
+    "status": {
+        "all": false,
+        "choices": [
+            "active"
+        ]
+    }
+}</t>
+  </si>
+  <si>
+    <t>Google Entitlement ID</t>
+  </si>
+  <si>
+    <t>Google Entitlement Status</t>
+  </si>
+  <si>
+    <t>Item Quantity</t>
+  </si>
+  <si>
+    <t>Google Offer ID</t>
+  </si>
+  <si>
+    <t>Google Creation Time</t>
+  </si>
+  <si>
+    <t>Google Commitment Start Date</t>
+  </si>
+  <si>
+    <t>Google Commitment End Date</t>
+  </si>
+  <si>
+    <t>Google Renewal Enabled</t>
+  </si>
+  <si>
+    <t>Google Maximum Units</t>
+  </si>
+  <si>
+    <t>Google Assigned Units</t>
+  </si>
+  <si>
+    <t>Google Num Units</t>
+  </si>
+  <si>
+    <t>Google Offer SKU Display Name</t>
+  </si>
+  <si>
+    <t>Google Offer Price</t>
+  </si>
+  <si>
+    <t>Google Offer Effective Price</t>
+  </si>
+  <si>
+    <t>Purchase Type</t>
+  </si>
+  <si>
+    <t>Google Suspension Reasons</t>
+  </si>
+  <si>
+    <t>Google Purchase Order ID</t>
+  </si>
+  <si>
+    <t>Error Details</t>
   </si>
   <si>
     <t>Consumption</t>
-  </si>
-  <si>
-    <t>Customer Name</t>
-  </si>
-  <si>
-    <t>Customer External ID</t>
-  </si>
-  <si>
-    <t>Customer Email</t>
-  </si>
-  <si>
-    <t>Tier 1 Name</t>
-  </si>
-  <si>
-    <t>Tier 1 External ID</t>
-  </si>
-  <si>
-    <t>Marketplace</t>
-  </si>
-  <si>
-    <t>Hub Name</t>
-  </si>
-  <si>
-    <t>Product Name</t>
-  </si>
-  <si>
-    <t>Subscription Status</t>
-  </si>
-  <si>
-    <t>Subscription Start Date</t>
-  </si>
-  <si>
-    <t>Subscription End Date</t>
-  </si>
-  <si>
-    <t>Exported At</t>
-  </si>
-  <si>
-    <t>Vendor Subscription Id</t>
-  </si>
-  <si>
-    <t>Price</t>
-  </si>
-  <si>
-    <t>Cost</t>
-  </si>
-  <si>
-    <t>Discount</t>
-  </si>
-  <si>
-    <t>Charge Type</t>
-  </si>
-  <si>
-    <t>Charge Date</t>
-  </si>
-  <si>
-    <t>Error Details</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -121,8 +291,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -133,6 +308,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1565C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,10 +328,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -454,34 +651,59 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:BA15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" outlineLevelCol="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="20.21875" customWidth="1"/>
-    <col min="3" max="6" width="18.77734375" customWidth="1"/>
-    <col min="11" max="14" width="17.21875" customWidth="1"/>
-    <col min="23" max="23" width="9.109375" customWidth="1"/>
-    <col min="24" max="24" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="26.33203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="2" max="20" width="20" style="3" customWidth="1"/>
+    <col min="21" max="24" width="18.83203125" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="25" max="26" width="25" style="4" customWidth="1" outlineLevel="1"/>
+    <col min="27" max="30" width="18.83203125" style="3" customWidth="1"/>
+    <col min="31" max="31" width="17.1640625" style="3" customWidth="1"/>
+    <col min="32" max="32" width="20" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="33" max="33" width="17.83203125" style="3" customWidth="1"/>
+    <col min="34" max="34" width="17.83203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="35" max="35" width="17.83203125" style="3" customWidth="1"/>
+    <col min="36" max="36" width="19.33203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="37" max="37" width="45.83203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="38" max="38" width="20" style="3" customWidth="1"/>
+    <col min="39" max="39" width="19.33203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="40" max="40" width="45.83203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="41" max="41" width="20" style="3" customWidth="1"/>
+    <col min="42" max="42" width="19.33203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="43" max="43" width="45.83203125" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="44" max="44" width="20" style="3" customWidth="1"/>
+    <col min="45" max="45" width="20" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="46" max="46" width="45.83203125" style="3" customWidth="1"/>
+    <col min="47" max="47" width="15" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="48" max="48" width="45.83203125" style="3" customWidth="1"/>
+    <col min="49" max="49" width="20" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="50" max="50" width="45.83203125" style="3" customWidth="1"/>
+    <col min="51" max="51" width="15" style="3" customWidth="1" outlineLevel="1"/>
+    <col min="52" max="52" width="45.83203125" style="3" customWidth="1"/>
+    <col min="53" max="53" width="18.6640625" style="3" customWidth="1"/>
+    <col min="54" max="54" width="8.83203125" style="3" customWidth="1"/>
+    <col min="55" max="16384" width="8.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -499,60 +721,332 @@
         <v>8</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="V1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="W1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AO1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="AP1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="AQ1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="U1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="V1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="W1" s="1" t="s">
+      <c r="AR1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AS1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="X1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z1" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="AA1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AT1" s="1" t="s">
         <v>27</v>
       </c>
+      <c r="AU1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U2" s="5"/>
+      <c r="V2" s="5"/>
+      <c r="W2" s="5"/>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U3" s="5"/>
+      <c r="V3" s="5"/>
+      <c r="W3" s="5"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U4" s="5"/>
+      <c r="V4" s="5"/>
+      <c r="W4" s="5"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U5" s="5"/>
+      <c r="V5" s="5"/>
+      <c r="W5" s="5"/>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U6" s="5"/>
+      <c r="V6" s="5"/>
+      <c r="W6" s="5"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U7" s="5"/>
+      <c r="V7" s="5"/>
+      <c r="W7" s="5"/>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U8" s="5"/>
+      <c r="V8" s="5"/>
+      <c r="W8" s="5"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U9" s="5"/>
+      <c r="V9" s="5"/>
+      <c r="W9" s="5"/>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U10" s="5"/>
+      <c r="V10" s="5"/>
+      <c r="W10" s="5"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U11" s="5"/>
+      <c r="V11" s="5"/>
+      <c r="W11" s="5"/>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U12" s="5"/>
+      <c r="V12" s="5"/>
+      <c r="W12" s="5"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U13" s="5"/>
+      <c r="V13" s="5"/>
+      <c r="W13" s="5"/>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U14" s="5"/>
+      <c r="V14" s="5"/>
+      <c r="W14" s="5"/>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.2">
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AA1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="50" customWidth="1"/>
+    <col min="2" max="2" width="180" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="31" x14ac:dyDescent="0.2">
+      <c r="A1" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="9"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>